--- a/Literature/BESS SA.xlsx
+++ b/Literature/BESS SA.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/webshape/Library/Mobile Documents/com~apple~CloudDocs/Dateien/UCL/Econometrics/Assessment/Literature/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E154FAE-3A49-0B49-8B7B-06C3F3C372CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8008CAEB-A361-A448-89DA-0D9157788F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{F9359397-F4F1-D047-8483-3AD39FC29116}"/>
+    <workbookView xWindow="5640" yWindow="10820" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{F9359397-F4F1-D047-8483-3AD39FC29116}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t>Name der Anlage</t>
   </si>
@@ -114,6 +115,48 @@
   </si>
   <si>
     <t>(Regelbetrieb gedrosselt*)</t>
+  </si>
+  <si>
+    <t>freigegebene Leistung (MW)</t>
+  </si>
+  <si>
+    <t>Quelle</t>
+  </si>
+  <si>
+    <t>https://hornsdalepowerreserve.com.au/</t>
+  </si>
+  <si>
+    <t>Hornsdale Power Reserve extension</t>
+  </si>
+  <si>
+    <t>https://arena.gov.au/blog/electranet-south-australian-battery-shows-the-way-forward/</t>
+  </si>
+  <si>
+    <t>https://arena.gov.au/knowledge-bank/lake-bonney-operational-report/</t>
+  </si>
+  <si>
+    <t>https://openelectricity.org.au/facilities?view=timeline&amp;statuses=operating,commissioning&amp;regions=sa1&amp;fuel_techs=battery&amp;capacity_min=2&amp;capacity_max=850&amp;facility=HORNSDPR</t>
+  </si>
+  <si>
+    <t>https://www.escosa.sa.gov.au/projects-and-publications/projects/electricity/electricity-generation-licence-variation-sa-water-christies-beach-treatment-plant</t>
+  </si>
+  <si>
+    <t>https://esdnews.com.au/vena-energy-celebrates-tailem-bend-2-commissioning/</t>
+  </si>
+  <si>
+    <t>https://nhoagroup.com/documents/blyth-battery-goes-live-nhoa-energy-and-elecnor-commission-the-477mwh-asset-for-neoen-in-south-australia/</t>
+  </si>
+  <si>
+    <t>https://epicenergy.com.au/2025/10/10/mannum-bess-commences-commercial-operations/</t>
+  </si>
+  <si>
+    <t>https://www.sma-australia.com.au/success-stories/torrens-island-battery-energy-storage-system</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>s p</t>
   </si>
 </sst>
 </file>
@@ -121,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -141,6 +184,21 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -162,24 +220,72 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -190,6 +296,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CA33EF9C-7BC5-D843-8BE7-A99C26FD7FEF}" name="Table1" displayName="Table1" ref="A1:F13" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:F13" xr:uid="{CA33EF9C-7BC5-D843-8BE7-A99C26FD7FEF}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{2763A2BA-F120-9A4C-9D9F-4F4489345B83}" name="Name der Anlage" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{35573FAE-CBA3-4348-978E-3C52F1E9D04C}" name="freigegebene Leistung (MW)"/>
+    <tableColumn id="3" xr3:uid="{613584EB-81BA-7345-BB7F-0BE84FBD890B}" name="Kapazität (MWh)"/>
+    <tableColumn id="4" xr3:uid="{AD7EE38E-F54B-DE4E-935A-137E823DDF7D}" name="Datum der ersten Einspeisung" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{A539123E-2A85-2042-8D8B-4669A3322C18}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{DE20F1C5-A00D-5B4F-9797-41D11537A4C6}" name="Quelle" dataCellStyle="Hyperlink"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -783,4 +904,279 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA82F0D-5F41-D543-AD03-6B163F69116A}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
+      </c>
+      <c r="D2" s="5">
+        <v>45931</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>238.5</v>
+      </c>
+      <c r="C3">
+        <v>477</v>
+      </c>
+      <c r="D3" s="5">
+        <v>45748</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <v>84</v>
+      </c>
+      <c r="D4" s="5">
+        <v>45658</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>250</v>
+      </c>
+      <c r="C5">
+        <v>250</v>
+      </c>
+      <c r="D5" s="5">
+        <v>45139</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>2.1</v>
+      </c>
+      <c r="C6">
+        <v>4.3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>44621</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D7" s="5">
+        <v>44713</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>44593</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5">
+        <v>44317</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>52</v>
+      </c>
+      <c r="D10" s="5">
+        <v>43800</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5">
+        <v>43435</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>129</v>
+      </c>
+      <c r="D12" s="5">
+        <v>43009</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+      <c r="C13">
+        <v>64.5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>44075</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F12" r:id="rId1" xr:uid="{4CEB9EFB-3909-734F-8D5B-2D62C16B57F1}"/>
+    <hyperlink ref="F13" r:id="rId2" xr:uid="{5CBD9CDA-9F10-2543-BB83-7F380535AAD3}"/>
+    <hyperlink ref="F11" r:id="rId3" xr:uid="{E57A5F65-730B-8944-ACA5-46C9BAC40736}"/>
+    <hyperlink ref="F10" r:id="rId4" xr:uid="{B997338D-5070-F64F-B553-342B499A0800}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{6EDEDE20-0E07-DB41-AD93-D89A8199BE43}"/>
+    <hyperlink ref="F2" r:id="rId6" xr:uid="{8D5F46AA-618A-0847-ACF9-BD8D7DE41403}"/>
+    <hyperlink ref="F3" r:id="rId7" xr:uid="{4844DFDA-1186-5948-9671-ED1FB313E60C}"/>
+    <hyperlink ref="F4" r:id="rId8" xr:uid="{E6207573-9B01-234D-9131-05A576B749B0}"/>
+    <hyperlink ref="F5" r:id="rId9" xr:uid="{ACDEA9B3-CC9A-A542-B49F-CF4B663CBCBC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId10"/>
+  </tableParts>
+</worksheet>
 </file>